--- a/res/tabela de nutrientes.xlsx
+++ b/res/tabela de nutrientes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/480d9b848b88e342/MSS/_Zoo-Rebio/ZooRebio3-23_24/rebio23-part/res/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_8EC6323DEB31E2B420E422BF073E1BAD2A5940E2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E5A83E15-331E-491E-8360-C15099983044}"/>
+  <xr:revisionPtr revIDLastSave="28" documentId="11_8EC6323DEB31E2B420E422BF073E1BAD2A5940E2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{56F72474-DB5E-4CA4-A0AE-CC6777F78D2C}"/>
   <bookViews>
     <workbookView xWindow="-21720" yWindow="-22425" windowWidth="21840" windowHeight="37920" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="106">
   <si>
     <t>Variable</t>
   </si>
@@ -273,16 +273,88 @@
   </si>
   <si>
     <t>16.4 (8.7-30.3)</t>
+  </si>
+  <si>
+    <t>Site 1</t>
+  </si>
+  <si>
+    <t>Site 2</t>
+  </si>
+  <si>
+    <t>Site 3</t>
+  </si>
+  <si>
+    <t>Site 4</t>
+  </si>
+  <si>
+    <t>Site 5</t>
+  </si>
+  <si>
+    <t>Site 6</t>
+  </si>
+  <si>
+    <t>Site 7</t>
+  </si>
+  <si>
+    <t>Site 8</t>
+  </si>
+  <si>
+    <t>Site 9</t>
+  </si>
+  <si>
+    <t>Site 10</t>
+  </si>
+  <si>
+    <t>Site 11</t>
+  </si>
+  <si>
+    <t>Site 12</t>
+  </si>
+  <si>
+    <t>Site 13</t>
+  </si>
+  <si>
+    <t>Site 14</t>
+  </si>
+  <si>
+    <t>Site 15</t>
+  </si>
+  <si>
+    <t>Ammonia (µg L⁻¹)</t>
+  </si>
+  <si>
+    <t>Nitrite (µg L⁻¹)</t>
+  </si>
+  <si>
+    <t>Nitrate (µg L⁻¹)</t>
+  </si>
+  <si>
+    <t>Orthophosphate (µg L⁻¹)</t>
+  </si>
+  <si>
+    <t>Phosphorus (µg L⁻¹)</t>
+  </si>
+  <si>
+    <t>Barro Branco strream</t>
+  </si>
+  <si>
+    <t>Caiana stream</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -308,8 +380,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -325,6 +400,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -917,310 +996,336 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4CB3E84-6953-43DE-8E0D-3696C6F82D61}">
-  <dimension ref="A1:P6"/>
+  <dimension ref="A1:P7"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.140625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" t="s">
-        <v>15</v>
-      </c>
+      <c r="B1" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>16</v>
-      </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>84</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="D2" t="s">
-        <v>19</v>
+        <v>86</v>
       </c>
       <c r="E2" t="s">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="F2" t="s">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="G2" t="s">
-        <v>22</v>
+        <v>89</v>
       </c>
       <c r="H2" t="s">
-        <v>23</v>
+        <v>90</v>
       </c>
       <c r="I2" t="s">
-        <v>24</v>
+        <v>91</v>
       </c>
       <c r="J2" t="s">
-        <v>25</v>
+        <v>92</v>
       </c>
       <c r="K2" t="s">
-        <v>26</v>
+        <v>93</v>
       </c>
       <c r="L2" t="s">
-        <v>27</v>
+        <v>94</v>
       </c>
       <c r="M2" t="s">
-        <v>28</v>
+        <v>95</v>
       </c>
       <c r="N2" t="s">
-        <v>29</v>
+        <v>96</v>
       </c>
       <c r="O2" t="s">
-        <v>30</v>
+        <v>97</v>
       </c>
       <c r="P2" t="s">
-        <v>31</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>32</v>
+        <v>99</v>
       </c>
       <c r="B3" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="D3" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="E3" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="F3" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="G3" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="H3" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="I3" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="J3" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="K3" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="L3" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="M3" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="N3" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="O3" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="P3" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D4" t="s">
-        <v>46</v>
-      </c>
-      <c r="E4" t="s">
-        <v>47</v>
-      </c>
-      <c r="F4" t="s">
-        <v>48</v>
-      </c>
-      <c r="G4" t="s">
-        <v>49</v>
+        <v>100</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="I4" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="J4" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="K4" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="L4" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="M4" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="N4" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="O4" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="P4" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>59</v>
+        <v>101</v>
       </c>
       <c r="B5" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D5" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="E5" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="F5" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="G5" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="H5" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="I5" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="J5" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="K5" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="L5" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="M5" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="N5" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="O5" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="P5" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>69</v>
-      </c>
-      <c r="B6" t="s">
-        <v>33</v>
-      </c>
-      <c r="C6" t="s">
+        <v>102</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6" t="s">
+        <v>60</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6" t="s">
+        <v>61</v>
+      </c>
+      <c r="I6" t="s">
+        <v>62</v>
+      </c>
+      <c r="J6" t="s">
+        <v>63</v>
+      </c>
+      <c r="K6" t="s">
+        <v>64</v>
+      </c>
+      <c r="L6" t="s">
+        <v>65</v>
+      </c>
+      <c r="M6" t="s">
+        <v>66</v>
+      </c>
+      <c r="N6" t="s">
+        <v>66</v>
+      </c>
+      <c r="O6" t="s">
+        <v>67</v>
+      </c>
+      <c r="P6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>103</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7" t="s">
         <v>70</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D7" t="s">
         <v>71</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E7" t="s">
         <v>72</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F7" t="s">
         <v>73</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G7" t="s">
         <v>74</v>
       </c>
-      <c r="H6" t="s">
+      <c r="H7" t="s">
         <v>75</v>
       </c>
-      <c r="I6" t="s">
+      <c r="I7" t="s">
         <v>76</v>
       </c>
-      <c r="J6" t="s">
+      <c r="J7" t="s">
         <v>77</v>
       </c>
-      <c r="K6" t="s">
+      <c r="K7" t="s">
         <v>78</v>
       </c>
-      <c r="L6" t="s">
+      <c r="L7" t="s">
         <v>79</v>
       </c>
-      <c r="M6" t="s">
+      <c r="M7" t="s">
         <v>80</v>
       </c>
-      <c r="N6" t="s">
+      <c r="N7" t="s">
         <v>81</v>
       </c>
-      <c r="O6" t="s">
+      <c r="O7" t="s">
         <v>82</v>
       </c>
-      <c r="P6" t="s">
+      <c r="P7" t="s">
         <v>83</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="H1:P1"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
--- a/res/tabela de nutrientes.xlsx
+++ b/res/tabela de nutrientes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/480d9b848b88e342/MSS/_Zoo-Rebio/ZooRebio3-23_24/rebio23-part/res/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="28" documentId="11_8EC6323DEB31E2B420E422BF073E1BAD2A5940E2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{56F72474-DB5E-4CA4-A0AE-CC6777F78D2C}"/>
+  <xr:revisionPtr revIDLastSave="54" documentId="11_8EC6323DEB31E2B420E422BF073E1BAD2A5940E2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{03F455EC-7D20-4329-ADB7-F25B5C3C3A77}"/>
   <bookViews>
     <workbookView xWindow="-21720" yWindow="-22425" windowWidth="21840" windowHeight="37920" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="113">
   <si>
     <t>Variable</t>
   </si>
@@ -339,13 +339,34 @@
   </si>
   <si>
     <t>Caiana stream</t>
+  </si>
+  <si>
+    <t>2003.0 (1652.6-2309.7)</t>
+  </si>
+  <si>
+    <t>644.0 (581.1-695.4)</t>
+  </si>
+  <si>
+    <t>1624.0 (322.6-4106.9)</t>
+  </si>
+  <si>
+    <t>6.0 (0-9.7)</t>
+  </si>
+  <si>
+    <t>1.0 (0-3)</t>
+  </si>
+  <si>
+    <t>4.0 (0.1-5.9)</t>
+  </si>
+  <si>
+    <t>13.0 (7.3-23)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -359,13 +380,33 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -380,10 +421,28 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1000,6 +1059,9 @@
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.140625" customWidth="1"/>
+    <col min="2" max="9" width="7" customWidth="1"/>
+    <col min="10" max="10" width="7.85546875" customWidth="1"/>
+    <col min="11" max="16" width="7" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
@@ -1024,299 +1086,299 @@
       <c r="P1" s="1"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L2" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="M2" t="s">
+      <c r="M2" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="N2" t="s">
+      <c r="N2" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="O2" t="s">
+      <c r="O2" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="P2" t="s">
+      <c r="P2" s="5" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>99</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J3" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="K3" t="s">
+      <c r="K3" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="L3" t="s">
+      <c r="L3" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="M3" t="s">
+      <c r="M3" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="N3" t="s">
+      <c r="N3" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="O3" t="s">
+      <c r="O3" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="P3" t="s">
+      <c r="P3" s="6" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>100</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="2">
         <v>0</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="2">
         <v>0</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="2">
         <v>0</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="2">
         <v>0</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="2">
         <v>0</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="2">
         <v>0</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="J4" t="s">
+      <c r="J4" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="K4" t="s">
+      <c r="K4" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="L4" t="s">
+      <c r="L4" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="M4" t="s">
+      <c r="M4" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="N4" t="s">
+      <c r="N4" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="O4" t="s">
+      <c r="O4" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="P4" t="s">
+      <c r="P4" s="5" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>101</v>
       </c>
-      <c r="B5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="B5" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H5" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="J5" t="s">
-        <v>52</v>
-      </c>
-      <c r="K5" t="s">
+      <c r="J5" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="K5" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="L5" t="s">
-        <v>54</v>
-      </c>
-      <c r="M5" t="s">
+      <c r="L5" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="M5" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="N5" t="s">
+      <c r="N5" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="O5" t="s">
-        <v>57</v>
-      </c>
-      <c r="P5" t="s">
+      <c r="O5" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="P5" s="6" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>102</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="2">
         <v>0</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="2">
         <v>0</v>
       </c>
-      <c r="D6" t="s">
-        <v>60</v>
-      </c>
-      <c r="E6">
+      <c r="D6" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E6" s="2">
         <v>0</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="2">
         <v>0</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="2">
         <v>0</v>
       </c>
-      <c r="H6" t="s">
+      <c r="H6" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="I6" t="s">
-        <v>62</v>
-      </c>
-      <c r="J6" t="s">
+      <c r="I6" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="J6" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="K6" t="s">
+      <c r="K6" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="L6" t="s">
+      <c r="L6" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="M6" t="s">
+      <c r="M6" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N6" t="s">
+      <c r="N6" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="O6" t="s">
+      <c r="O6" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="P6" t="s">
-        <v>68</v>
+      <c r="P6" s="5" t="s">
+        <v>112</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>103</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="2">
         <v>0</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="G7" t="s">
+      <c r="G7" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="H7" t="s">
+      <c r="H7" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="I7" t="s">
+      <c r="I7" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="J7" t="s">
+      <c r="J7" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="K7" t="s">
+      <c r="K7" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="L7" t="s">
+      <c r="L7" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="M7" t="s">
+      <c r="M7" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="N7" t="s">
+      <c r="N7" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="O7" t="s">
+      <c r="O7" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="P7" t="s">
+      <c r="P7" s="5" t="s">
         <v>83</v>
       </c>
     </row>

--- a/res/tabela de nutrientes.xlsx
+++ b/res/tabela de nutrientes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/480d9b848b88e342/MSS/_Zoo-Rebio/ZooRebio3-23_24/rebio23-part/res/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="54" documentId="11_8EC6323DEB31E2B420E422BF073E1BAD2A5940E2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{03F455EC-7D20-4329-ADB7-F25B5C3C3A77}"/>
+  <xr:revisionPtr revIDLastSave="62" documentId="11_8EC6323DEB31E2B420E422BF073E1BAD2A5940E2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B7672DA9-897E-4FBD-9598-AFBAC5A4A9E4}"/>
   <bookViews>
-    <workbookView xWindow="-21720" yWindow="-22425" windowWidth="21840" windowHeight="37920" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20490" yWindow="-21510" windowWidth="19470" windowHeight="13380" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -421,7 +421,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -443,6 +443,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1065,7 +1068,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="8" t="s">
         <v>104</v>
       </c>
       <c r="C1" s="1"/>
@@ -1073,7 +1076,7 @@
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="8" t="s">
         <v>105</v>
       </c>
       <c r="I1" s="1"/>
@@ -1132,7 +1135,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>99</v>
       </c>
@@ -1182,7 +1185,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>100</v>
       </c>
@@ -1332,7 +1335,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>103</v>
       </c>
@@ -1383,10 +1386,6 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="B1:G1"/>
-    <mergeCell ref="H1:P1"/>
-  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
